--- a/analysis/dataview/binary-tree.xlsx
+++ b/analysis/dataview/binary-tree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="58">
   <si>
     <t>Unique Variants</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>hierarchy</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
   <si>
     <t>01-ai</t>
@@ -642,10 +645,10 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>87.29601694915254</v>
+        <v>38.98521186440678</v>
       </c>
       <c r="C2">
-        <v>28.27726333142238</v>
+        <v>37.63763229316866</v>
       </c>
       <c r="D2">
         <v>236</v>
@@ -656,10 +659,10 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>8.31156779661017</v>
+        <v>33.79648305084746</v>
       </c>
       <c r="C3">
-        <v>17.47681373656589</v>
+        <v>35.71859141518346</v>
       </c>
       <c r="D3">
         <v>236</v>
@@ -670,10 +673,10 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>9.061101694915255</v>
+        <v>10.33033898305085</v>
       </c>
       <c r="C4">
-        <v>18.08980948743634</v>
+        <v>20.78446633271264</v>
       </c>
       <c r="D4">
         <v>236</v>
@@ -684,10 +687,10 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>9.221991525423729</v>
+        <v>32.43296610169492</v>
       </c>
       <c r="C5">
-        <v>19.04215321321811</v>
+        <v>36.04700168861861</v>
       </c>
       <c r="D5">
         <v>236</v>
@@ -698,10 +701,10 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>17.55550847457627</v>
+        <v>45.8235593220339</v>
       </c>
       <c r="C6">
-        <v>28.5397260300097</v>
+        <v>40.3730410583423</v>
       </c>
       <c r="D6">
         <v>236</v>
@@ -750,10 +753,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>27.73069306930693</v>
+        <v>27.37758132956153</v>
       </c>
       <c r="C2">
-        <v>36.41017765755046</v>
+        <v>33.14164702260904</v>
       </c>
       <c r="D2">
         <v>707</v>
@@ -764,10 +767,10 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>29.08090523338048</v>
+        <v>39.42224893917963</v>
       </c>
       <c r="C3">
-        <v>36.64250920787332</v>
+        <v>35.72484955223757</v>
       </c>
       <c r="D3">
         <v>707</v>
@@ -802,10 +805,10 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>38.28133333333334</v>
+        <v>48.0816875</v>
       </c>
       <c r="C2">
-        <v>35.63046664782966</v>
+        <v>35.67631929034626</v>
       </c>
       <c r="D2">
         <v>480</v>
@@ -816,10 +819,10 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>22.11231277533039</v>
+        <v>19.60394273127753</v>
       </c>
       <c r="C3">
-        <v>35.7294682971044</v>
+        <v>29.46794621206198</v>
       </c>
       <c r="D3">
         <v>454</v>
@@ -830,10 +833,10 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>24.48285416666667</v>
+        <v>31.76683333333333</v>
       </c>
       <c r="C4">
-        <v>36.14898679527883</v>
+        <v>33.37586758309285</v>
       </c>
       <c r="D4">
         <v>480</v>
@@ -868,13 +871,13 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>21.33161458333333</v>
+        <v>31.4430753968254</v>
       </c>
       <c r="C2">
-        <v>34.24927652167489</v>
+        <v>32.09306712239166</v>
       </c>
       <c r="D2">
-        <v>576</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -882,13 +885,13 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>17.61608450704225</v>
+        <v>23.74681818181818</v>
       </c>
       <c r="C3">
-        <v>31.27903945212921</v>
+        <v>29.68641918805043</v>
       </c>
       <c r="D3">
-        <v>710</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -896,13 +899,13 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>20.18560763888889</v>
+        <v>30.14855158730159</v>
       </c>
       <c r="C4">
-        <v>32.81043032958792</v>
+        <v>33.23680828741699</v>
       </c>
       <c r="D4">
-        <v>576</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -934,10 +937,10 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>29.92955431754874</v>
+        <v>32.22303621169916</v>
       </c>
       <c r="C2">
-        <v>37.24574911874043</v>
+        <v>34.89743097530978</v>
       </c>
       <c r="D2">
         <v>718</v>
@@ -948,10 +951,10 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>26.83387931034483</v>
+        <v>34.61399425287356</v>
       </c>
       <c r="C3">
-        <v>35.71418848947395</v>
+        <v>35.02455574556326</v>
       </c>
       <c r="D3">
         <v>696</v>
@@ -964,161 +967,224 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B2">
-        <v>20.85875</v>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
       </c>
       <c r="C2">
-        <v>35.69819058568023</v>
+        <v>26.17666666666667</v>
       </c>
       <c r="D2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3">
-        <v>27.14127314814815</v>
+        <v>34.47174564606969</v>
+      </c>
+      <c r="E2">
+        <v>72</v>
+      </c>
+      <c r="F2">
+        <v>26.17666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>35.73023691723686</v>
+        <v>27.89368055555556</v>
       </c>
       <c r="D3">
+        <v>31.89476806326628</v>
+      </c>
+      <c r="E3">
         <v>432</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4">
-        <v>27.81013888888889</v>
+      <c r="F3">
+        <v>45.60902777777778</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>36.38665188213538</v>
+        <v>36.71555555555555</v>
       </c>
       <c r="D4">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5">
-        <v>3.217666666666667</v>
+        <v>32.10811252359529</v>
+      </c>
+      <c r="E4">
+        <v>72</v>
+      </c>
+      <c r="F4">
+        <v>32.84898148148148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>6.976029993002957</v>
+        <v>2.623666666666666</v>
       </c>
       <c r="D5">
+        <v>5.992481720885034</v>
+      </c>
+      <c r="E5">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6">
-        <v>48.32777777777778</v>
+      <c r="F5">
+        <v>2.623666666666666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>38.91026567981598</v>
+        <v>70.22902777777777</v>
       </c>
       <c r="D6">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7">
-        <v>26.47888888888889</v>
+        <v>32.15134142426252</v>
+      </c>
+      <c r="E6">
+        <v>72</v>
+      </c>
+      <c r="F6">
+        <v>70.22902777777777</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>36.2048833977771</v>
+        <v>34.27902777777778</v>
       </c>
       <c r="D7">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8">
-        <v>28.06072222222222</v>
+        <v>31.5826877679387</v>
+      </c>
+      <c r="E7">
+        <v>72</v>
+      </c>
+      <c r="F7">
+        <v>34.27902777777778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>36.43326742092187</v>
+        <v>35.06441666666667</v>
       </c>
       <c r="D8">
+        <v>35.78659790523431</v>
+      </c>
+      <c r="E8">
         <v>360</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9">
-        <v>26.69241379310345</v>
+      <c r="F8">
+        <v>64.48694444444445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
       </c>
       <c r="C9">
-        <v>36.54640560291035</v>
+        <v>27.36293103448276</v>
       </c>
       <c r="D9">
+        <v>31.40059737998183</v>
+      </c>
+      <c r="E9">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10">
-        <v>25.875</v>
+      <c r="F9">
+        <v>27.36293103448276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
       </c>
       <c r="C10">
-        <v>35.90425322994478</v>
+        <v>26.14486111111111</v>
       </c>
       <c r="D10">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11">
-        <v>40.58645833333333</v>
+        <v>29.60911312859823</v>
+      </c>
+      <c r="E10">
+        <v>72</v>
+      </c>
+      <c r="F10">
+        <v>26.14486111111111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>38.17611013802976</v>
+        <v>47.73958333333334</v>
       </c>
       <c r="D11">
+        <v>37.2589369178021</v>
+      </c>
+      <c r="E11">
         <v>144</v>
+      </c>
+      <c r="F11">
+        <v>56.27175925925926</v>
       </c>
     </row>
   </sheetData>
@@ -1147,13 +1213,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2">
-        <v>3.217666666666667</v>
+        <v>2.623666666666666</v>
       </c>
       <c r="C2">
-        <v>6.976029993002957</v>
+        <v>5.992481720885034</v>
       </c>
       <c r="D2">
         <v>60</v>
@@ -1161,13 +1227,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3">
-        <v>48.74597222222222</v>
+        <v>64.48694444444445</v>
       </c>
       <c r="C3">
-        <v>37.47750354920813</v>
+        <v>31.80616928547964</v>
       </c>
       <c r="D3">
         <v>72</v>
@@ -1175,13 +1241,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4">
-        <v>39.77625</v>
+        <v>54.73263888888889</v>
       </c>
       <c r="C4">
-        <v>37.24837466678112</v>
+        <v>36.05609733332236</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -1189,13 +1255,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5">
-        <v>13.5675</v>
+        <v>9.574444444444445</v>
       </c>
       <c r="C5">
-        <v>29.72987617404323</v>
+        <v>20.06708993049466</v>
       </c>
       <c r="D5">
         <v>72</v>
@@ -1203,13 +1269,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6">
-        <v>25.68791666666667</v>
+        <v>31.79027777777778</v>
       </c>
       <c r="C6">
-        <v>37.51557494167223</v>
+        <v>29.9716623426817</v>
       </c>
       <c r="D6">
         <v>72</v>
@@ -1217,13 +1283,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7">
-        <v>12.52597222222222</v>
+        <v>14.73777777777778</v>
       </c>
       <c r="C7">
-        <v>24.32831067809522</v>
+        <v>22.44934286325939</v>
       </c>
       <c r="D7">
         <v>72</v>
@@ -1231,13 +1297,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8">
-        <v>25.875</v>
+        <v>26.14486111111111</v>
       </c>
       <c r="C8">
-        <v>35.90425322994478</v>
+        <v>29.60911312859823</v>
       </c>
       <c r="D8">
         <v>72</v>
@@ -1245,13 +1311,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9">
-        <v>26.69241379310345</v>
+        <v>27.36293103448276</v>
       </c>
       <c r="C9">
-        <v>36.54640560291035</v>
+        <v>31.40059737998183</v>
       </c>
       <c r="D9">
         <v>58</v>
@@ -1259,13 +1325,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10">
-        <v>3.729444444444444</v>
+        <v>1.986944444444444</v>
       </c>
       <c r="C10">
-        <v>9.726795556589385</v>
+        <v>5.368971532874221</v>
       </c>
       <c r="D10">
         <v>72</v>
@@ -1273,13 +1339,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11">
-        <v>21.49597222222222</v>
+        <v>19.42527777777778</v>
       </c>
       <c r="C11">
-        <v>31.83752550100882</v>
+        <v>21.06342086445841</v>
       </c>
       <c r="D11">
         <v>72</v>
@@ -1287,13 +1353,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12">
-        <v>40.85027777777778</v>
+        <v>42.90791666666667</v>
       </c>
       <c r="C12">
-        <v>39.00256957848507</v>
+        <v>35.19738934531014</v>
       </c>
       <c r="D12">
         <v>72</v>
@@ -1301,13 +1367,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13">
-        <v>27.19916666666667</v>
+        <v>24.32444444444444</v>
       </c>
       <c r="C13">
-        <v>37.44614960743674</v>
+        <v>28.30171566435798</v>
       </c>
       <c r="D13">
         <v>72</v>
@@ -1315,13 +1381,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14">
-        <v>40.10402777777777</v>
+        <v>45.60902777777778</v>
       </c>
       <c r="C14">
-        <v>37.01324143188478</v>
+        <v>35.10009073298822</v>
       </c>
       <c r="D14">
         <v>72</v>
@@ -1329,13 +1395,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15">
-        <v>29.46875</v>
+        <v>33.10847222222222</v>
       </c>
       <c r="C15">
-        <v>37.33012829735766</v>
+        <v>33.01901729710961</v>
       </c>
       <c r="D15">
         <v>72</v>
@@ -1343,13 +1409,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16">
-        <v>20.85875</v>
+        <v>26.17666666666667</v>
       </c>
       <c r="C16">
-        <v>35.69819058568023</v>
+        <v>34.47174564606969</v>
       </c>
       <c r="D16">
         <v>72</v>
@@ -1357,13 +1423,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17">
-        <v>48.32777777777778</v>
+        <v>70.22902777777777</v>
       </c>
       <c r="C17">
-        <v>38.91026567981598</v>
+        <v>32.15134142426252</v>
       </c>
       <c r="D17">
         <v>72</v>
@@ -1371,13 +1437,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18">
-        <v>27.81013888888889</v>
+        <v>36.71555555555555</v>
       </c>
       <c r="C18">
-        <v>36.38665188213538</v>
+        <v>32.10811252359529</v>
       </c>
       <c r="D18">
         <v>72</v>
@@ -1385,13 +1451,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19">
-        <v>31.51972222222222</v>
+        <v>39.19069444444445</v>
       </c>
       <c r="C19">
-        <v>37.03046431312598</v>
+        <v>36.63290721551117</v>
       </c>
       <c r="D19">
         <v>72</v>
@@ -1399,13 +1465,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20">
-        <v>49.65319444444444</v>
+        <v>56.28847222222223</v>
       </c>
       <c r="C20">
-        <v>37.38148471517623</v>
+        <v>36.13604418281442</v>
       </c>
       <c r="D20">
         <v>72</v>
@@ -1413,13 +1479,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21">
-        <v>26.47888888888889</v>
+        <v>34.27902777777778</v>
       </c>
       <c r="C21">
-        <v>36.2048833977771</v>
+        <v>31.5826877679387</v>
       </c>
       <c r="D21">
         <v>72</v>
